--- a/Result/profitability/2317.xlsx
+++ b/Result/profitability/2317.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>2.56</v>
       </c>
       <c r="M2" t="n">
-        <v>3.32875</v>
+        <v>3.41875</v>
       </c>
       <c r="N2" t="n">
-        <v>6.53375</v>
+        <v>6.525</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1.61</v>
       </c>
       <c r="M3" t="n">
-        <v>3.08625</v>
+        <v>3.2025</v>
       </c>
       <c r="N3" t="n">
-        <v>6.797499999999999</v>
+        <v>6.79375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>2.4</v>
       </c>
       <c r="M4" t="n">
-        <v>2.96875</v>
+        <v>3.12375</v>
       </c>
       <c r="N4" t="n">
-        <v>7.171250000000001</v>
+        <v>7.1725</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>1.26</v>
       </c>
       <c r="M5" t="n">
-        <v>2.7475</v>
+        <v>2.8825</v>
       </c>
       <c r="N5" t="n">
-        <v>7.40375</v>
+        <v>7.3775</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>1.8</v>
       </c>
       <c r="M6" t="n">
-        <v>2.57375</v>
+        <v>2.58875</v>
       </c>
       <c r="N6" t="n">
-        <v>7.7975</v>
+        <v>7.768750000000001</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.76</v>
       </c>
       <c r="M7" t="n">
-        <v>2.275</v>
+        <v>2.4025</v>
       </c>
       <c r="N7" t="n">
-        <v>8.15625</v>
+        <v>8.186249999999999</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>2.14</v>
       </c>
       <c r="M8" t="n">
-        <v>2.13625</v>
+        <v>2.225</v>
       </c>
       <c r="N8" t="n">
-        <v>8.547499999999999</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2317</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2525894</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2371361</v>
+      </c>
+      <c r="E75" t="n">
+        <v>154533</v>
+      </c>
+      <c r="F75" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="G75" t="n">
+        <v>94803</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>3.75%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>63</v>
+      </c>
+      <c r="J75" t="n">
+        <v>94866</v>
+      </c>
+      <c r="K75" t="n">
+        <v>59974</v>
+      </c>
+      <c r="L75" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="M75" t="n">
+        <v>3.5425</v>
+      </c>
+      <c r="N75" t="n">
+        <v>6.163749999999999</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.7099999999999995</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.1994382022471908</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.05999999999999961</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.009708737864077555</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.3385579937304075</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.03317535545023698</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
